--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
@@ -59,13 +59,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
@@ -29,7 +29,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-problems</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/ValueSet/at-aps-problems</t>
   </si>
   <si>
     <t>Version</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-problems.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
